--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122708338</v>
+        <v>136663253</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>87410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillhägnen, Lillhägnen, Jmt</t>
+          <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483260</v>
+        <v>483296</v>
       </c>
       <c r="R2" t="n">
-        <v>6991371</v>
+        <v>6991353</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,97 +761,73 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122708338</t>
+          <t>https://artportalen.se/Sighting/136663253</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133059563</v>
+        <v>136663280</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>89332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483242</v>
+        <v>483221</v>
       </c>
       <c r="R3" t="n">
-        <v>6991402</v>
+        <v>6991464</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,72 +865,75 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059563</t>
+          <t>https://artportalen.se/Sighting/136663280</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133059573</v>
+        <v>136663330</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>89332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Löfsåsen, Jmt</t>
+          <t>Backvallen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483225</v>
+        <v>483264</v>
       </c>
       <c r="R4" t="n">
-        <v>6991633</v>
+        <v>6991388</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,69 +977,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059573</t>
+          <t>https://artportalen.se/Sighting/136663330</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133059560</v>
+        <v>136663323</v>
       </c>
       <c r="B5" t="n">
-        <v>80488</v>
+        <v>91614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5747</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Löfsåsen, Jmt</t>
+          <t>Backvallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483344</v>
+        <v>483339</v>
       </c>
       <c r="R5" t="n">
-        <v>6991330</v>
+        <v>6991443</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,27 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 bål</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,62 +1083,66 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059560</t>
+          <t>https://artportalen.se/Sighting/136663323</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133059574</v>
+        <v>136663315</v>
       </c>
       <c r="B6" t="n">
-        <v>58349</v>
+        <v>91622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>5754</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Löfsåsen, Jmt</t>
+          <t>Backvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483226</v>
+        <v>483243</v>
       </c>
       <c r="R6" t="n">
-        <v>6991635</v>
+        <v>6991442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,22 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,65 +1189,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059574</t>
+          <t>https://artportalen.se/Sighting/136663315</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133059569</v>
+        <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>104707</v>
+        <v>93436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Löfsåsen, Jmt</t>
+          <t>Backvallen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483225</v>
+        <v>483406</v>
       </c>
       <c r="R7" t="n">
-        <v>6991627</v>
+        <v>6991505</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,22 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,65 +1295,69 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059569</t>
+          <t>https://artportalen.se/Sighting/136663307</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133059565</v>
+        <v>122708338</v>
       </c>
       <c r="B8" t="n">
-        <v>101403</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Löfsåsen, Jmt</t>
+          <t>Lillhägnen, Lillhägnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483196</v>
+        <v>483260</v>
       </c>
       <c r="R8" t="n">
-        <v>6991546</v>
+        <v>6991371</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,22 +1381,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,69 +1397,97 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059565</t>
+          <t>https://artportalen.se/Sighting/122708338</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133059566</v>
+        <v>133059563</v>
       </c>
       <c r="B9" t="n">
-        <v>101403</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483202</v>
+        <v>483242</v>
       </c>
       <c r="R9" t="n">
-        <v>6991548</v>
+        <v>6991402</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,6 +1535,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1598,38 +1553,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059566</t>
+          <t>https://artportalen.se/Sighting/133059563</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133059568</v>
+        <v>133059573</v>
       </c>
       <c r="B10" t="n">
-        <v>101403</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1639,13 +1594,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483221</v>
+        <v>483225</v>
       </c>
       <c r="R10" t="n">
-        <v>6991568</v>
+        <v>6991633</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1674,7 +1629,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1639,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,54 +1665,58 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059568</t>
+          <t>https://artportalen.se/Sighting/133059573</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133059570</v>
+        <v>133059560</v>
       </c>
       <c r="B11" t="n">
-        <v>101403</v>
+        <v>80488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483224</v>
+        <v>483344</v>
       </c>
       <c r="R11" t="n">
-        <v>6991630</v>
+        <v>6991330</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1786,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1755,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 bål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,7 +1786,785 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/133059560</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133059574</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>483226</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6991635</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059574</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133059569</v>
+      </c>
+      <c r="B13" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>483225</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6991627</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059569</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133059565</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>483196</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6991546</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059565</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133059566</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>483202</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6991548</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059566</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133059568</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>483221</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6991568</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059568</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133059570</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>483224</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6991630</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/133059570</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136663255</v>
+      </c>
+      <c r="B18" t="n">
+        <v>87469</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6003296</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stor odörspindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius mussivus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>483312</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6991443</v>
+      </c>
+      <c r="S18" t="n">
+        <v>100</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663255</t>
         </is>
       </c>
     </row>
@@ -1838,6 +2580,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663253</v>
       </c>
       <c r="B2" t="n">
-        <v>87410</v>
+        <v>87412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663280</v>
       </c>
       <c r="B3" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663330</v>
       </c>
       <c r="B4" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663323</v>
       </c>
       <c r="B5" t="n">
-        <v>91614</v>
+        <v>91616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663315</v>
       </c>
       <c r="B6" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136663255</v>
       </c>
       <c r="B18" t="n">
-        <v>87469</v>
+        <v>87471</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663253</v>
       </c>
       <c r="B2" t="n">
-        <v>87412</v>
+        <v>87414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663280</v>
       </c>
       <c r="B3" t="n">
-        <v>89334</v>
+        <v>89336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663330</v>
       </c>
       <c r="B4" t="n">
-        <v>89334</v>
+        <v>89336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663323</v>
       </c>
       <c r="B5" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663315</v>
       </c>
       <c r="B6" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136663255</v>
       </c>
       <c r="B18" t="n">
-        <v>87471</v>
+        <v>87473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663253</v>
       </c>
       <c r="B2" t="n">
-        <v>87414</v>
+        <v>87416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663280</v>
       </c>
       <c r="B3" t="n">
-        <v>89336</v>
+        <v>89338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663330</v>
       </c>
       <c r="B4" t="n">
-        <v>89336</v>
+        <v>89338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663323</v>
       </c>
       <c r="B5" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663315</v>
       </c>
       <c r="B6" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136663255</v>
       </c>
       <c r="B18" t="n">
-        <v>87473</v>
+        <v>87475</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663253</v>
       </c>
       <c r="B2" t="n">
-        <v>87416</v>
+        <v>87418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663280</v>
       </c>
       <c r="B3" t="n">
-        <v>89338</v>
+        <v>89340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663330</v>
       </c>
       <c r="B4" t="n">
-        <v>89338</v>
+        <v>89340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663323</v>
       </c>
       <c r="B5" t="n">
-        <v>91620</v>
+        <v>91622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663315</v>
       </c>
       <c r="B6" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136663255</v>
       </c>
       <c r="B18" t="n">
-        <v>87475</v>
+        <v>87477</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663253</v>
       </c>
       <c r="B2" t="n">
-        <v>87418</v>
+        <v>87420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663280</v>
       </c>
       <c r="B3" t="n">
-        <v>89340</v>
+        <v>89342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663330</v>
       </c>
       <c r="B4" t="n">
-        <v>89340</v>
+        <v>89342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663323</v>
       </c>
       <c r="B5" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663315</v>
       </c>
       <c r="B6" t="n">
-        <v>91630</v>
+        <v>91632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136663255</v>
       </c>
       <c r="B18" t="n">
-        <v>87477</v>
+        <v>87479</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663253</v>
       </c>
       <c r="B2" t="n">
-        <v>87420</v>
+        <v>87421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663280</v>
       </c>
       <c r="B3" t="n">
-        <v>89342</v>
+        <v>89343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663330</v>
       </c>
       <c r="B4" t="n">
-        <v>89342</v>
+        <v>89343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663323</v>
       </c>
       <c r="B5" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663315</v>
       </c>
       <c r="B6" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136663255</v>
       </c>
       <c r="B18" t="n">
-        <v>87479</v>
+        <v>87480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663253</v>
       </c>
       <c r="B2" t="n">
-        <v>87421</v>
+        <v>87427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663280</v>
       </c>
       <c r="B3" t="n">
-        <v>89343</v>
+        <v>89349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663330</v>
       </c>
       <c r="B4" t="n">
-        <v>89343</v>
+        <v>89349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663323</v>
       </c>
       <c r="B5" t="n">
-        <v>91625</v>
+        <v>91631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663315</v>
       </c>
       <c r="B6" t="n">
-        <v>91633</v>
+        <v>91639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136663255</v>
       </c>
       <c r="B18" t="n">
-        <v>87480</v>
+        <v>87486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663253</v>
       </c>
       <c r="B2" t="n">
-        <v>87427</v>
+        <v>87431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663280</v>
       </c>
       <c r="B3" t="n">
-        <v>89349</v>
+        <v>89353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663330</v>
       </c>
       <c r="B4" t="n">
-        <v>89349</v>
+        <v>89353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663323</v>
       </c>
       <c r="B5" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663315</v>
       </c>
       <c r="B6" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136663255</v>
       </c>
       <c r="B18" t="n">
-        <v>87486</v>
+        <v>87490</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663253</v>
       </c>
       <c r="B2" t="n">
-        <v>87431</v>
+        <v>87433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663280</v>
       </c>
       <c r="B3" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663330</v>
       </c>
       <c r="B4" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663323</v>
       </c>
       <c r="B5" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663315</v>
       </c>
       <c r="B6" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136663255</v>
       </c>
       <c r="B18" t="n">
-        <v>87490</v>
+        <v>87492</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663253</v>
       </c>
       <c r="B2" t="n">
-        <v>87433</v>
+        <v>87446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663280</v>
       </c>
       <c r="B3" t="n">
-        <v>89355</v>
+        <v>89368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663330</v>
       </c>
       <c r="B4" t="n">
-        <v>89355</v>
+        <v>89368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663323</v>
       </c>
       <c r="B5" t="n">
-        <v>91637</v>
+        <v>91650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663315</v>
       </c>
       <c r="B6" t="n">
-        <v>91645</v>
+        <v>91658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136663255</v>
       </c>
       <c r="B18" t="n">
-        <v>87492</v>
+        <v>87505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663253</v>
       </c>
       <c r="B2" t="n">
-        <v>87446</v>
+        <v>87448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663280</v>
       </c>
       <c r="B3" t="n">
-        <v>89368</v>
+        <v>89370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663330</v>
       </c>
       <c r="B4" t="n">
-        <v>89368</v>
+        <v>89370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663323</v>
       </c>
       <c r="B5" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663315</v>
       </c>
       <c r="B6" t="n">
-        <v>91658</v>
+        <v>91660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136663255</v>
       </c>
       <c r="B18" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663253</v>
       </c>
       <c r="B2" t="n">
-        <v>87448</v>
+        <v>87451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663280</v>
       </c>
       <c r="B3" t="n">
-        <v>89370</v>
+        <v>89373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663330</v>
       </c>
       <c r="B4" t="n">
-        <v>89370</v>
+        <v>89373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663323</v>
       </c>
       <c r="B5" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663315</v>
       </c>
       <c r="B6" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663307</v>
       </c>
       <c r="B7" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136663255</v>
       </c>
       <c r="B18" t="n">
-        <v>87507</v>
+        <v>87510</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136663280</v>
+        <v>137389271</v>
       </c>
       <c r="B3" t="n">
-        <v>89373</v>
+        <v>87549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4412</v>
+        <v>1988</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483221</v>
+        <v>483192</v>
       </c>
       <c r="R3" t="n">
-        <v>6991464</v>
+        <v>6991517</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,21 +881,21 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136663280</t>
+          <t>https://artportalen.se/Sighting/137389271</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136663330</v>
+        <v>137389272</v>
       </c>
       <c r="B4" t="n">
-        <v>89373</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backvallen, Jmt</t>
+          <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483264</v>
+        <v>483210</v>
       </c>
       <c r="R4" t="n">
-        <v>6991388</v>
+        <v>6991538</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,59 +987,59 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136663330</t>
+          <t>https://artportalen.se/Sighting/137389272</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136663323</v>
+        <v>137389274</v>
       </c>
       <c r="B5" t="n">
-        <v>91655</v>
+        <v>93463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5747</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Backvallen, Jmt</t>
+          <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483339</v>
+        <v>483200</v>
       </c>
       <c r="R5" t="n">
-        <v>6991443</v>
+        <v>6991555</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,21 +1093,21 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136663323</t>
+          <t>https://artportalen.se/Sighting/137389274</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136663315</v>
+        <v>136663280</v>
       </c>
       <c r="B6" t="n">
-        <v>91663</v>
+        <v>89373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5754</v>
+        <v>4412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Backvallen, Jmt</t>
+          <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483243</v>
+        <v>483221</v>
       </c>
       <c r="R6" t="n">
-        <v>6991442</v>
+        <v>6991464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,16 +1204,16 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136663315</t>
+          <t>https://artportalen.se/Sighting/136663280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136663307</v>
+        <v>136663330</v>
       </c>
       <c r="B7" t="n">
-        <v>93481</v>
+        <v>89373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483406</v>
+        <v>483264</v>
       </c>
       <c r="R7" t="n">
-        <v>6991505</v>
+        <v>6991388</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,54 +1310,54 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136663307</t>
+          <t>https://artportalen.se/Sighting/136663330</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122708338</v>
+        <v>137389262</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>89387</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillhägnen, Lillhägnen, Jmt</t>
+          <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483260</v>
+        <v>483211</v>
       </c>
       <c r="R8" t="n">
-        <v>6991371</v>
+        <v>6991475</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,97 +1397,73 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122708338</t>
+          <t>https://artportalen.se/Sighting/137389262</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133059563</v>
+        <v>137389264</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>89387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483242</v>
+        <v>483236</v>
       </c>
       <c r="R9" t="n">
-        <v>6991402</v>
+        <v>6991524</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,22 +1487,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,56 +1501,59 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059563</t>
+          <t>https://artportalen.se/Sighting/137389264</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133059573</v>
+        <v>137389203</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>93134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,13 +1563,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483225</v>
+        <v>483252</v>
       </c>
       <c r="R10" t="n">
-        <v>6991633</v>
+        <v>6991404</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1624,22 +1593,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,69 +1613,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059573</t>
+          <t>https://artportalen.se/Sighting/137389203</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133059560</v>
+        <v>136663323</v>
       </c>
       <c r="B11" t="n">
-        <v>80488</v>
+        <v>91655</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>5747</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Löfsåsen, Jmt</t>
+          <t>Backvallen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483344</v>
+        <v>483339</v>
       </c>
       <c r="R11" t="n">
-        <v>6991330</v>
+        <v>6991443</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,27 +1699,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1 bål</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,49 +1719,53 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059560</t>
+          <t>https://artportalen.se/Sighting/136663323</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133059574</v>
+        <v>137389265</v>
       </c>
       <c r="B12" t="n">
-        <v>58349</v>
+        <v>91671</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>5747</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1775,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483226</v>
+        <v>483250</v>
       </c>
       <c r="R12" t="n">
-        <v>6991635</v>
+        <v>6991554</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,22 +1805,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,65 +1825,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059574</t>
+          <t>https://artportalen.se/Sighting/137389265</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133059569</v>
+        <v>136663315</v>
       </c>
       <c r="B13" t="n">
-        <v>104707</v>
+        <v>91663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>5754</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Löfsåsen, Jmt</t>
+          <t>Backvallen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483225</v>
+        <v>483243</v>
       </c>
       <c r="R13" t="n">
-        <v>6991627</v>
+        <v>6991442</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1969,22 +1911,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,49 +1931,53 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059569</t>
+          <t>https://artportalen.se/Sighting/136663315</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133059565</v>
+        <v>137389268</v>
       </c>
       <c r="B14" t="n">
-        <v>101403</v>
+        <v>91679</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>5754</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2051,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483196</v>
+        <v>483268</v>
       </c>
       <c r="R14" t="n">
-        <v>6991546</v>
+        <v>6991406</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,22 +2017,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,65 +2037,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059565</t>
+          <t>https://artportalen.se/Sighting/137389268</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133059566</v>
+        <v>136663307</v>
       </c>
       <c r="B15" t="n">
-        <v>101403</v>
+        <v>93481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Löfsåsen, Jmt</t>
+          <t>Backvallen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483202</v>
+        <v>483406</v>
       </c>
       <c r="R15" t="n">
-        <v>6991548</v>
+        <v>6991505</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,22 +2123,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:48</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:48</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,49 +2143,53 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059566</t>
+          <t>https://artportalen.se/Sighting/136663307</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133059568</v>
+        <v>137389202</v>
       </c>
       <c r="B16" t="n">
-        <v>101403</v>
+        <v>93499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,13 +2199,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483221</v>
+        <v>483264</v>
       </c>
       <c r="R16" t="n">
-        <v>6991568</v>
+        <v>6991412</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2305,22 +2229,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,49 +2249,53 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059568</t>
+          <t>https://artportalen.se/Sighting/137389202</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133059570</v>
+        <v>137389205</v>
       </c>
       <c r="B17" t="n">
-        <v>101403</v>
+        <v>93499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2387,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483224</v>
+        <v>483187</v>
       </c>
       <c r="R17" t="n">
-        <v>6991630</v>
+        <v>6991498</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2417,22 +2335,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,27 +2355,31 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133059570</t>
+          <t>https://artportalen.se/Sighting/137389205</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136663255</v>
+        <v>122708338</v>
       </c>
       <c r="B18" t="n">
-        <v>87510</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,37 +2387,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6003296</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Löfsåsen, Jmt</t>
+          <t>Lillhägnen, Lillhägnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483312</v>
+        <v>483260</v>
       </c>
       <c r="R18" t="n">
-        <v>6991443</v>
+        <v>6991371</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,12 +2441,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,26 +2457,2028 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122708338</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133059563</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>483242</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6991402</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059563</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133059573</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>483225</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6991633</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059573</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137389269</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79516</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>483279</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6991437</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>på många träd inom detta område med k-skog</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137389269</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133059560</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>483344</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6991330</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1 bål</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059560</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133059574</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>483226</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6991635</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059574</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137389270</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>483342</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6991508</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137389270</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133059569</v>
+      </c>
+      <c r="B25" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>483225</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6991627</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059569</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133059565</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>483196</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6991546</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059565</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133059566</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>483202</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6991548</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059566</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133059568</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>483221</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6991568</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059568</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133059570</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>483224</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6991630</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059570</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137389199</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101530</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>483364</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6991324</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137389199</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137389206</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101530</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>483154</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6991506</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137389206</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137389267</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101530</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>483419</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6991349</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137389267</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137389201</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90902</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>245031</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Borgsjömusseron</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tricholoma borgsjoeënse</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Jacobsson &amp; Muskos</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>483276</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6991387</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137389201</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137389260</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91656</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>483250</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6991412</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137389260</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136663255</v>
+      </c>
+      <c r="B35" t="n">
+        <v>87510</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6003296</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Stor odörspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius mussivus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>483312</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6991443</v>
+      </c>
+      <c r="S35" t="n">
+        <v>100</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136663255</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137389209</v>
+      </c>
+      <c r="B36" t="n">
+        <v>87524</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6003296</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Stor odörspindling</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cortinarius mussivus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>483266</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6991507</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137389209</t>
         </is>
       </c>
     </row>
@@ -2587,6 +4501,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137389271</v>
       </c>
       <c r="B3" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137389272</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137389274</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137389262</v>
       </c>
       <c r="B8" t="n">
-        <v>89387</v>
+        <v>89392</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137389264</v>
       </c>
       <c r="B9" t="n">
-        <v>89387</v>
+        <v>89392</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>137389203</v>
       </c>
       <c r="B10" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>137389265</v>
       </c>
       <c r="B12" t="n">
-        <v>91671</v>
+        <v>91676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>137389268</v>
       </c>
       <c r="B14" t="n">
-        <v>91679</v>
+        <v>91684</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>137389202</v>
       </c>
       <c r="B16" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137389205</v>
       </c>
       <c r="B17" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137389269</v>
       </c>
       <c r="B21" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>137389270</v>
       </c>
       <c r="B24" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>137389199</v>
       </c>
       <c r="B30" t="n">
-        <v>101530</v>
+        <v>101536</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>137389206</v>
       </c>
       <c r="B31" t="n">
-        <v>101530</v>
+        <v>101536</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>137389267</v>
       </c>
       <c r="B32" t="n">
-        <v>101530</v>
+        <v>101536</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>137389201</v>
       </c>
       <c r="B33" t="n">
-        <v>90902</v>
+        <v>90907</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>137389260</v>
       </c>
       <c r="B34" t="n">
-        <v>91656</v>
+        <v>91661</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>137389209</v>
       </c>
       <c r="B36" t="n">
-        <v>87524</v>
+        <v>87529</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137389271</v>
       </c>
       <c r="B3" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137389272</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137389274</v>
       </c>
       <c r="B5" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137389262</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
+        <v>89403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137389264</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
+        <v>89403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>137389203</v>
       </c>
       <c r="B10" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>137389265</v>
       </c>
       <c r="B12" t="n">
-        <v>91676</v>
+        <v>91688</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>137389268</v>
       </c>
       <c r="B14" t="n">
-        <v>91684</v>
+        <v>91696</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>137389202</v>
       </c>
       <c r="B16" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137389205</v>
       </c>
       <c r="B17" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137389269</v>
       </c>
       <c r="B21" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>137389199</v>
       </c>
       <c r="B30" t="n">
-        <v>101536</v>
+        <v>101548</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>137389206</v>
       </c>
       <c r="B31" t="n">
-        <v>101536</v>
+        <v>101548</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>137389267</v>
       </c>
       <c r="B32" t="n">
-        <v>101536</v>
+        <v>101548</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>137389201</v>
       </c>
       <c r="B33" t="n">
-        <v>90907</v>
+        <v>90918</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>137389260</v>
       </c>
       <c r="B34" t="n">
-        <v>91661</v>
+        <v>91673</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>137389209</v>
       </c>
       <c r="B36" t="n">
-        <v>87529</v>
+        <v>87540</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137389271</v>
       </c>
       <c r="B3" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137389272</v>
       </c>
       <c r="B4" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137389274</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137389262</v>
       </c>
       <c r="B8" t="n">
-        <v>89403</v>
+        <v>89404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137389264</v>
       </c>
       <c r="B9" t="n">
-        <v>89403</v>
+        <v>89404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>137389203</v>
       </c>
       <c r="B10" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>137389265</v>
       </c>
       <c r="B12" t="n">
-        <v>91688</v>
+        <v>91689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>137389268</v>
       </c>
       <c r="B14" t="n">
-        <v>91696</v>
+        <v>91697</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>137389202</v>
       </c>
       <c r="B16" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137389205</v>
       </c>
       <c r="B17" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137389269</v>
       </c>
       <c r="B21" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>137389199</v>
       </c>
       <c r="B30" t="n">
-        <v>101548</v>
+        <v>101549</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>137389206</v>
       </c>
       <c r="B31" t="n">
-        <v>101548</v>
+        <v>101549</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>137389267</v>
       </c>
       <c r="B32" t="n">
-        <v>101548</v>
+        <v>101549</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>137389201</v>
       </c>
       <c r="B33" t="n">
-        <v>90918</v>
+        <v>90919</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>137389260</v>
       </c>
       <c r="B34" t="n">
-        <v>91673</v>
+        <v>91674</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>137389209</v>
       </c>
       <c r="B36" t="n">
-        <v>87540</v>
+        <v>87541</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137389271</v>
       </c>
       <c r="B3" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137389272</v>
       </c>
       <c r="B4" t="n">
-        <v>93474</v>
+        <v>93477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137389274</v>
       </c>
       <c r="B5" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137389262</v>
       </c>
       <c r="B8" t="n">
-        <v>89404</v>
+        <v>89407</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137389264</v>
       </c>
       <c r="B9" t="n">
-        <v>89404</v>
+        <v>89407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>137389203</v>
       </c>
       <c r="B10" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>137389265</v>
       </c>
       <c r="B12" t="n">
-        <v>91689</v>
+        <v>91692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>137389268</v>
       </c>
       <c r="B14" t="n">
-        <v>91697</v>
+        <v>91700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>137389202</v>
       </c>
       <c r="B16" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137389205</v>
       </c>
       <c r="B17" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137389269</v>
       </c>
       <c r="B21" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>137389199</v>
       </c>
       <c r="B30" t="n">
-        <v>101549</v>
+        <v>101552</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>137389206</v>
       </c>
       <c r="B31" t="n">
-        <v>101549</v>
+        <v>101552</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>137389267</v>
       </c>
       <c r="B32" t="n">
-        <v>101549</v>
+        <v>101552</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>137389201</v>
       </c>
       <c r="B33" t="n">
-        <v>90919</v>
+        <v>90922</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>137389260</v>
       </c>
       <c r="B34" t="n">
-        <v>91674</v>
+        <v>91677</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>137389209</v>
       </c>
       <c r="B36" t="n">
-        <v>87541</v>
+        <v>87544</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137389271</v>
       </c>
       <c r="B3" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137389272</v>
       </c>
       <c r="B4" t="n">
-        <v>93477</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137389274</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137389262</v>
       </c>
       <c r="B8" t="n">
-        <v>89407</v>
+        <v>89411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137389264</v>
       </c>
       <c r="B9" t="n">
-        <v>89407</v>
+        <v>89411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>137389203</v>
       </c>
       <c r="B10" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>137389265</v>
       </c>
       <c r="B12" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>137389268</v>
       </c>
       <c r="B14" t="n">
-        <v>91700</v>
+        <v>91704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>137389202</v>
       </c>
       <c r="B16" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137389205</v>
       </c>
       <c r="B17" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>137389269</v>
       </c>
       <c r="B21" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>137389270</v>
       </c>
       <c r="B24" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>137389199</v>
       </c>
       <c r="B30" t="n">
-        <v>101552</v>
+        <v>101556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>137389206</v>
       </c>
       <c r="B31" t="n">
-        <v>101552</v>
+        <v>101556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>137389267</v>
       </c>
       <c r="B32" t="n">
-        <v>101552</v>
+        <v>101556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>137389201</v>
       </c>
       <c r="B33" t="n">
-        <v>90922</v>
+        <v>90926</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>137389260</v>
       </c>
       <c r="B34" t="n">
-        <v>91677</v>
+        <v>91681</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>137389209</v>
       </c>
       <c r="B36" t="n">
-        <v>87544</v>
+        <v>87548</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
